--- a/reports/Planning-G012.xlsx
+++ b/reports/Planning-G012.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aitan\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pablo Murillo\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D589C80D-A95D-4490-80CF-039D93FFBD3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CDCC5D28-629C-4412-8EF1-E35D30084EE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14914" firstSheet="2" activeTab="2" xr2:uid="{683E09B8-1D94-4905-B116-9D998A46AAA3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="3" activeTab="3" xr2:uid="{683E09B8-1D94-4905-B116-9D998A46AAA3}"/>
   </bookViews>
   <sheets>
     <sheet name="Copyright" sheetId="10" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="168">
   <si>
     <t>Copyright</t>
   </si>
@@ -388,9 +388,63 @@
     <t>Fix getMonthsActive</t>
   </si>
   <si>
+    <t>Fix  internationalisation in Boolean and Select</t>
+  </si>
+  <si>
+    <t>Fix validations in student 2</t>
+  </si>
+  <si>
     <t>Deliverable D02</t>
   </si>
   <si>
+    <t>Rewrite requirements in analysis report and data model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implement role Manager </t>
+  </si>
+  <si>
+    <t>Implement entity Project + additional constraints (keywords and dates)</t>
+  </si>
+  <si>
+    <t>Implement squad ProjectMember</t>
+  </si>
+  <si>
+    <t>manager: CRUD projects + publish Projects</t>
+  </si>
+  <si>
+    <t>manager: create projectmembers</t>
+  </si>
+  <si>
+    <t>projectmember: Display projects + components</t>
+  </si>
+  <si>
+    <t>projectmember: add components to a project</t>
+  </si>
+  <si>
+    <t>Dashboard + effort</t>
+  </si>
+  <si>
+    <t>Sponsor/auditor attaching to a project</t>
+  </si>
+  <si>
+    <t>Advertisement</t>
+  </si>
+  <si>
+    <t>Sample and errata for Manager</t>
+  </si>
+  <si>
+    <t>Sample and errata for Project</t>
+  </si>
+  <si>
+    <t>Link components to projects on sample and errata (key:project on each component's csv)</t>
+  </si>
+  <si>
+    <t>Sample and errata for ProjectMembership and ProjectMember</t>
+  </si>
+  <si>
+    <t>ManagerDashboard feature</t>
+  </si>
+  <si>
     <t>Deliverable D03</t>
   </si>
   <si>
@@ -509,12 +563,6 @@
   </si>
   <si>
     <t>O</t>
-  </si>
-  <si>
-    <t>Fix  internationalisation in Boolean and Select</t>
-  </si>
-  <si>
-    <t>Fix validations in student 2</t>
   </si>
 </sst>
 </file>
@@ -789,7 +837,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -903,17 +951,18 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1553,124 +1602,124 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0BB59C7-21D2-4063-B60E-B9743CBEBCDD}">
   <dimension ref="B2:J12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B2" s="57" t="s">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B2" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B4" s="58" t="s">
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B4" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="59"/>
-      <c r="D4" s="59"/>
-      <c r="E4" s="59"/>
-      <c r="F4" s="59"/>
-      <c r="G4" s="59"/>
-      <c r="H4" s="59"/>
-      <c r="I4" s="59"/>
-      <c r="J4" s="59"/>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B5" s="59"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="59"/>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B6" s="59"/>
-      <c r="C6" s="59"/>
-      <c r="D6" s="59"/>
-      <c r="E6" s="59"/>
-      <c r="F6" s="59"/>
-      <c r="G6" s="59"/>
-      <c r="H6" s="59"/>
-      <c r="I6" s="59"/>
-      <c r="J6" s="59"/>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B7" s="59"/>
-      <c r="C7" s="59"/>
-      <c r="D7" s="59"/>
-      <c r="E7" s="59"/>
-      <c r="F7" s="59"/>
-      <c r="G7" s="59"/>
-      <c r="H7" s="59"/>
-      <c r="I7" s="59"/>
-      <c r="J7" s="59"/>
-    </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B8" s="59"/>
-      <c r="C8" s="59"/>
-      <c r="D8" s="59"/>
-      <c r="E8" s="59"/>
-      <c r="F8" s="59"/>
-      <c r="G8" s="59"/>
-      <c r="H8" s="59"/>
-      <c r="I8" s="59"/>
-      <c r="J8" s="59"/>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B9" s="59"/>
-      <c r="C9" s="59"/>
-      <c r="D9" s="59"/>
-      <c r="E9" s="59"/>
-      <c r="F9" s="59"/>
-      <c r="G9" s="59"/>
-      <c r="H9" s="59"/>
-      <c r="I9" s="59"/>
-      <c r="J9" s="59"/>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B10" s="59"/>
-      <c r="C10" s="59"/>
-      <c r="D10" s="59"/>
-      <c r="E10" s="59"/>
-      <c r="F10" s="59"/>
-      <c r="G10" s="59"/>
-      <c r="H10" s="59"/>
-      <c r="I10" s="59"/>
-      <c r="J10" s="59"/>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B11" s="59"/>
-      <c r="C11" s="59"/>
-      <c r="D11" s="59"/>
-      <c r="E11" s="59"/>
-      <c r="F11" s="59"/>
-      <c r="G11" s="59"/>
-      <c r="H11" s="59"/>
-      <c r="I11" s="59"/>
-      <c r="J11" s="59"/>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B12" s="59"/>
-      <c r="C12" s="59"/>
-      <c r="D12" s="59"/>
-      <c r="E12" s="59"/>
-      <c r="F12" s="59"/>
-      <c r="G12" s="59"/>
-      <c r="H12" s="59"/>
-      <c r="I12" s="59"/>
-      <c r="J12" s="59"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="60"/>
+      <c r="H4" s="60"/>
+      <c r="I4" s="60"/>
+      <c r="J4" s="60"/>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B5" s="60"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
+      <c r="J5" s="60"/>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B6" s="60"/>
+      <c r="C6" s="60"/>
+      <c r="D6" s="60"/>
+      <c r="E6" s="60"/>
+      <c r="F6" s="60"/>
+      <c r="G6" s="60"/>
+      <c r="H6" s="60"/>
+      <c r="I6" s="60"/>
+      <c r="J6" s="60"/>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B7" s="60"/>
+      <c r="C7" s="60"/>
+      <c r="D7" s="60"/>
+      <c r="E7" s="60"/>
+      <c r="F7" s="60"/>
+      <c r="G7" s="60"/>
+      <c r="H7" s="60"/>
+      <c r="I7" s="60"/>
+      <c r="J7" s="60"/>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B8" s="60"/>
+      <c r="C8" s="60"/>
+      <c r="D8" s="60"/>
+      <c r="E8" s="60"/>
+      <c r="F8" s="60"/>
+      <c r="G8" s="60"/>
+      <c r="H8" s="60"/>
+      <c r="I8" s="60"/>
+      <c r="J8" s="60"/>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B9" s="60"/>
+      <c r="C9" s="60"/>
+      <c r="D9" s="60"/>
+      <c r="E9" s="60"/>
+      <c r="F9" s="60"/>
+      <c r="G9" s="60"/>
+      <c r="H9" s="60"/>
+      <c r="I9" s="60"/>
+      <c r="J9" s="60"/>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B10" s="60"/>
+      <c r="C10" s="60"/>
+      <c r="D10" s="60"/>
+      <c r="E10" s="60"/>
+      <c r="F10" s="60"/>
+      <c r="G10" s="60"/>
+      <c r="H10" s="60"/>
+      <c r="I10" s="60"/>
+      <c r="J10" s="60"/>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B11" s="60"/>
+      <c r="C11" s="60"/>
+      <c r="D11" s="60"/>
+      <c r="E11" s="60"/>
+      <c r="F11" s="60"/>
+      <c r="G11" s="60"/>
+      <c r="H11" s="60"/>
+      <c r="I11" s="60"/>
+      <c r="J11" s="60"/>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B12" s="60"/>
+      <c r="C12" s="60"/>
+      <c r="D12" s="60"/>
+      <c r="E12" s="60"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="60"/>
+      <c r="H12" s="60"/>
+      <c r="I12" s="60"/>
+      <c r="J12" s="60"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1685,22 +1734,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BB35E99-EEE5-419C-812A-054E20454F46}">
   <dimension ref="B2:J12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.3046875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B2" s="57" t="s">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B2" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-    </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="2"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -1711,42 +1760,42 @@
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
     </row>
-    <row r="4" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="58" t="s">
+    <row r="4" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B5" s="58"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="58"/>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B6" s="58"/>
-      <c r="C6" s="58"/>
-      <c r="D6" s="58"/>
-      <c r="E6" s="58"/>
-      <c r="F6" s="58"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="58"/>
-      <c r="I6" s="58"/>
-      <c r="J6" s="58"/>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B5" s="57"/>
+      <c r="C5" s="57"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="57"/>
+      <c r="H5" s="57"/>
+      <c r="I5" s="57"/>
+      <c r="J5" s="57"/>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B6" s="57"/>
+      <c r="C6" s="57"/>
+      <c r="D6" s="57"/>
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="57"/>
+      <c r="H6" s="57"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -1757,7 +1806,7 @@
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B8" s="39"/>
       <c r="C8" s="40" t="s">
         <v>4</v>
@@ -1770,33 +1819,33 @@
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="4"/>
-      <c r="C9" s="60" t="s">
+      <c r="C9" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="60"/>
-      <c r="E9" s="60"/>
-      <c r="F9" s="60"/>
-      <c r="G9" s="60"/>
-      <c r="H9" s="60"/>
-      <c r="I9" s="60"/>
-      <c r="J9" s="60"/>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="D9" s="61"/>
+      <c r="E9" s="61"/>
+      <c r="F9" s="61"/>
+      <c r="G9" s="61"/>
+      <c r="H9" s="61"/>
+      <c r="I9" s="61"/>
+      <c r="J9" s="61"/>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B10" s="49"/>
-      <c r="C10" s="60" t="s">
+      <c r="C10" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="60"/>
-      <c r="E10" s="60"/>
-      <c r="F10" s="60"/>
-      <c r="G10" s="60"/>
-      <c r="H10" s="60"/>
-      <c r="I10" s="60"/>
-      <c r="J10" s="60"/>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="D10" s="61"/>
+      <c r="E10" s="61"/>
+      <c r="F10" s="61"/>
+      <c r="G10" s="61"/>
+      <c r="H10" s="61"/>
+      <c r="I10" s="61"/>
+      <c r="J10" s="61"/>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="50"/>
       <c r="C11" s="48" t="s">
         <v>7</v>
@@ -1809,18 +1858,18 @@
       <c r="I11" s="48"/>
       <c r="J11" s="48"/>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B12" s="3"/>
-      <c r="C12" s="60" t="s">
+      <c r="C12" s="61" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="60"/>
-      <c r="E12" s="60"/>
-      <c r="F12" s="60"/>
-      <c r="G12" s="60"/>
-      <c r="H12" s="60"/>
-      <c r="I12" s="60"/>
-      <c r="J12" s="60"/>
+      <c r="D12" s="61"/>
+      <c r="E12" s="61"/>
+      <c r="F12" s="61"/>
+      <c r="G12" s="61"/>
+      <c r="H12" s="61"/>
+      <c r="I12" s="61"/>
+      <c r="J12" s="61"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1837,49 +1886,49 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34CF3CD5-8D08-494F-856F-AF84E30F468A}">
   <dimension ref="B2:P110"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.3046875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="15" width="18.69140625" customWidth="1"/>
-    <col min="16" max="16" width="64.53515625" customWidth="1"/>
+    <col min="3" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="64.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:16" x14ac:dyDescent="0.4">
-      <c r="C2" s="57" t="s">
+    <row r="2" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="C2" s="56" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="57"/>
-      <c r="L2" s="57"/>
-      <c r="M2" s="57"/>
-      <c r="N2" s="57"/>
-      <c r="O2" s="57"/>
-      <c r="P2" s="57"/>
-    </row>
-    <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C4" s="58" t="s">
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="56"/>
+      <c r="M2" s="56"/>
+      <c r="N2" s="56"/>
+      <c r="O2" s="56"/>
+      <c r="P2" s="56"/>
+    </row>
+    <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C4" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="58"/>
-      <c r="L4" s="58"/>
-      <c r="M4" s="58"/>
-      <c r="N4" s="58"/>
-      <c r="O4" s="58"/>
-      <c r="P4" s="58"/>
-    </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="57"/>
+      <c r="L4" s="57"/>
+      <c r="M4" s="57"/>
+      <c r="N4" s="57"/>
+      <c r="O4" s="57"/>
+      <c r="P4" s="57"/>
+    </row>
+    <row r="5" spans="2:16" x14ac:dyDescent="0.25">
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
@@ -1895,8 +1944,8 @@
       <c r="O5" s="5"/>
       <c r="P5" s="5"/>
     </row>
-    <row r="6" spans="2:16" x14ac:dyDescent="0.4">
-      <c r="C6" s="55" t="s">
+    <row r="6" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="C6" s="58" t="s">
         <v>11</v>
       </c>
       <c r="D6" s="10" t="s">
@@ -1918,8 +1967,8 @@
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
     </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.4">
-      <c r="C7" s="55"/>
+    <row r="7" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="C7" s="58"/>
       <c r="D7" s="11" t="s">
         <v>13</v>
       </c>
@@ -1929,7 +1978,7 @@
       </c>
       <c r="J7" s="37"/>
     </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B9" s="6"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -1937,22 +1986,22 @@
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
-      <c r="I9" s="56" t="s">
+      <c r="I9" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="J9" s="56"/>
+      <c r="J9" s="59"/>
       <c r="K9" s="7"/>
-      <c r="L9" s="56" t="s">
+      <c r="L9" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="M9" s="56"/>
-      <c r="N9" s="56" t="s">
+      <c r="M9" s="59"/>
+      <c r="N9" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="O9" s="56"/>
+      <c r="O9" s="59"/>
       <c r="P9" s="7"/>
     </row>
-    <row r="10" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="8" t="s">
         <v>17</v>
       </c>
@@ -1999,7 +2048,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="41">
         <v>1</v>
       </c>
@@ -2048,7 +2097,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="41">
         <v>2</v>
       </c>
@@ -2097,7 +2146,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="41">
         <v>3</v>
       </c>
@@ -2146,7 +2195,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="14" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="41">
         <v>4</v>
       </c>
@@ -2197,7 +2246,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="41">
         <v>5</v>
       </c>
@@ -2248,7 +2297,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="41">
         <v>6</v>
       </c>
@@ -2299,7 +2348,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="41">
         <v>7</v>
       </c>
@@ -2348,7 +2397,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="41">
         <v>8</v>
       </c>
@@ -2389,7 +2438,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="19" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="41">
         <v>9</v>
       </c>
@@ -2440,7 +2489,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="20" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="41">
         <v>10</v>
       </c>
@@ -2491,7 +2540,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="21" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="41">
         <v>11</v>
       </c>
@@ -2532,7 +2581,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="22" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="41">
         <v>12</v>
       </c>
@@ -2583,7 +2632,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="23" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B23" s="41">
         <v>13</v>
       </c>
@@ -2634,7 +2683,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="41">
         <v>14</v>
       </c>
@@ -2675,7 +2724,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="25" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B25" s="41">
         <v>15</v>
       </c>
@@ -2726,7 +2775,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="41">
         <v>16</v>
       </c>
@@ -2777,7 +2826,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B27" s="41">
         <v>17</v>
       </c>
@@ -2818,7 +2867,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="28" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B28" s="41">
         <v>18</v>
       </c>
@@ -2869,7 +2918,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="29" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B29" s="41">
         <v>19</v>
       </c>
@@ -2920,7 +2969,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="30" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="41">
         <v>20</v>
       </c>
@@ -2961,7 +3010,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="31" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B31" s="41">
         <v>21</v>
       </c>
@@ -3011,7 +3060,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="32" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B32" s="41">
         <v>22</v>
       </c>
@@ -3062,7 +3111,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="33" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="41">
         <v>23</v>
       </c>
@@ -3113,7 +3162,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="34" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B34" s="41">
         <v>24</v>
       </c>
@@ -3162,7 +3211,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="35" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B35" s="41">
         <v>25</v>
       </c>
@@ -3211,7 +3260,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="41">
         <v>26</v>
       </c>
@@ -3260,7 +3309,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="37" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="41">
         <v>27</v>
       </c>
@@ -3309,7 +3358,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="38" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B38" s="41">
         <v>28</v>
       </c>
@@ -3358,7 +3407,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="39" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B39" s="41">
         <v>29</v>
       </c>
@@ -3407,7 +3456,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="40" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B40" s="41">
         <v>30</v>
       </c>
@@ -3456,7 +3505,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="41" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B41" s="41">
         <v>31</v>
       </c>
@@ -3505,7 +3554,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="42" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B42" s="41">
         <v>32</v>
       </c>
@@ -3554,7 +3603,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="43" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B43" s="41">
         <v>33</v>
       </c>
@@ -3603,7 +3652,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="44" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B44" s="41">
         <v>34</v>
       </c>
@@ -3652,7 +3701,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="45" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B45" s="41">
         <v>35</v>
       </c>
@@ -3701,7 +3750,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="46" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B46" s="41">
         <v>36</v>
       </c>
@@ -3750,7 +3799,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="47" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B47" s="41">
         <v>37</v>
       </c>
@@ -3799,7 +3848,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="48" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B48" s="41">
         <v>38</v>
       </c>
@@ -3848,7 +3897,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="49" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B49" s="41">
         <v>39</v>
       </c>
@@ -3897,7 +3946,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="50" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B50" s="41">
         <v>40</v>
       </c>
@@ -3946,7 +3995,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="51" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B51" s="41">
         <v>41</v>
       </c>
@@ -3995,7 +4044,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="52" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B52" s="41">
         <v>42</v>
       </c>
@@ -4044,7 +4093,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="53" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B53" s="41">
         <v>43</v>
       </c>
@@ -4093,7 +4142,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="54" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B54" s="41">
         <v>44</v>
       </c>
@@ -4142,7 +4191,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="55" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="55" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B55" s="41">
         <v>45</v>
       </c>
@@ -4191,7 +4240,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="56" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B56" s="41">
         <v>46</v>
       </c>
@@ -4240,7 +4289,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="57" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B57" s="41">
         <v>47</v>
       </c>
@@ -4289,7 +4338,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="58" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B58" s="41">
         <v>48</v>
       </c>
@@ -4338,7 +4387,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="59" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B59" s="41">
         <v>49</v>
       </c>
@@ -4387,7 +4436,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="60" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B60" s="41">
         <v>50</v>
       </c>
@@ -4436,7 +4485,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="61" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B61" s="41">
         <v>51</v>
       </c>
@@ -4485,7 +4534,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="62" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B62" s="41">
         <v>52</v>
       </c>
@@ -4534,7 +4583,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="63" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B63" s="41">
         <v>53</v>
       </c>
@@ -4583,7 +4632,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="64" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B64" s="41">
         <v>54</v>
       </c>
@@ -4632,7 +4681,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="65" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B65" s="41">
         <v>55</v>
       </c>
@@ -4681,7 +4730,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="66" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B66" s="41">
         <v>56</v>
       </c>
@@ -4730,7 +4779,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="67" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B67" s="41">
         <v>57</v>
       </c>
@@ -4779,7 +4828,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="68" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B68" s="41">
         <v>58</v>
       </c>
@@ -4828,7 +4877,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="69" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B69" s="41">
         <v>59</v>
       </c>
@@ -4877,7 +4926,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="70" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B70" s="41">
         <v>60</v>
       </c>
@@ -4926,7 +4975,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="71" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B71" s="41">
         <v>61</v>
       </c>
@@ -4975,7 +5024,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="72" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B72" s="41">
         <v>62</v>
       </c>
@@ -5024,7 +5073,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="73" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B73" s="41">
         <v>63</v>
       </c>
@@ -5073,7 +5122,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="74" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B74" s="41">
         <v>64</v>
       </c>
@@ -5122,7 +5171,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="75" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B75" s="41">
         <v>65</v>
       </c>
@@ -5171,7 +5220,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="76" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B76" s="41">
         <v>66</v>
       </c>
@@ -5220,7 +5269,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="77" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B77" s="41">
         <v>67</v>
       </c>
@@ -5266,10 +5315,10 @@
         <v>25</v>
       </c>
       <c r="P77" s="44" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="78" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="78" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B78" s="41">
         <v>68</v>
       </c>
@@ -5315,10 +5364,10 @@
         <v>48</v>
       </c>
       <c r="P78" s="44" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="79" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B79" s="41">
         <v>69</v>
       </c>
@@ -5349,7 +5398,7 @@
       </c>
       <c r="P79" s="44"/>
     </row>
-    <row r="80" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B80" s="41">
         <v>70</v>
       </c>
@@ -5377,7 +5426,7 @@
       </c>
       <c r="P80" s="44"/>
     </row>
-    <row r="81" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B81" s="41">
         <v>71</v>
       </c>
@@ -5408,7 +5457,7 @@
       </c>
       <c r="P81" s="44"/>
     </row>
-    <row r="82" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B82" s="41">
         <v>72</v>
       </c>
@@ -5439,7 +5488,7 @@
       </c>
       <c r="P82" s="44"/>
     </row>
-    <row r="83" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B83" s="41">
         <v>73</v>
       </c>
@@ -5470,7 +5519,7 @@
       </c>
       <c r="P83" s="44"/>
     </row>
-    <row r="84" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B84" s="41">
         <v>74</v>
       </c>
@@ -5501,7 +5550,7 @@
       </c>
       <c r="P84" s="44"/>
     </row>
-    <row r="85" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B85" s="41">
         <v>75</v>
       </c>
@@ -5532,7 +5581,7 @@
       </c>
       <c r="P85" s="44"/>
     </row>
-    <row r="86" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B86" s="41">
         <v>76</v>
       </c>
@@ -5563,7 +5612,7 @@
       </c>
       <c r="P86" s="44"/>
     </row>
-    <row r="87" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B87" s="41">
         <v>77</v>
       </c>
@@ -5594,7 +5643,7 @@
       </c>
       <c r="P87" s="44"/>
     </row>
-    <row r="88" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B88" s="41">
         <v>78</v>
       </c>
@@ -5625,7 +5674,7 @@
       </c>
       <c r="P88" s="44"/>
     </row>
-    <row r="89" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B89" s="41">
         <v>79</v>
       </c>
@@ -5656,7 +5705,7 @@
       </c>
       <c r="P89" s="44"/>
     </row>
-    <row r="90" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B90" s="41">
         <v>80</v>
       </c>
@@ -5687,7 +5736,7 @@
       </c>
       <c r="P90" s="44"/>
     </row>
-    <row r="91" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="91" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B91" s="41">
         <v>81</v>
       </c>
@@ -5718,7 +5767,7 @@
       </c>
       <c r="P91" s="44"/>
     </row>
-    <row r="92" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B92" s="41">
         <v>82</v>
       </c>
@@ -5749,7 +5798,7 @@
       </c>
       <c r="P92" s="44"/>
     </row>
-    <row r="93" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="93" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B93" s="41">
         <v>83</v>
       </c>
@@ -5780,7 +5829,7 @@
       </c>
       <c r="P93" s="44"/>
     </row>
-    <row r="94" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B94" s="41">
         <v>84</v>
       </c>
@@ -5811,7 +5860,7 @@
       </c>
       <c r="P94" s="44"/>
     </row>
-    <row r="95" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="95" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B95" s="41">
         <v>85</v>
       </c>
@@ -5842,7 +5891,7 @@
       </c>
       <c r="P95" s="44"/>
     </row>
-    <row r="96" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B96" s="41">
         <v>86</v>
       </c>
@@ -5873,7 +5922,7 @@
       </c>
       <c r="P96" s="44"/>
     </row>
-    <row r="97" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B97" s="41">
         <v>87</v>
       </c>
@@ -5904,7 +5953,7 @@
       </c>
       <c r="P97" s="44"/>
     </row>
-    <row r="98" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="98" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B98" s="41">
         <v>88</v>
       </c>
@@ -5935,7 +5984,7 @@
       </c>
       <c r="P98" s="44"/>
     </row>
-    <row r="99" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B99" s="41">
         <v>89</v>
       </c>
@@ -5966,7 +6015,7 @@
       </c>
       <c r="P99" s="44"/>
     </row>
-    <row r="100" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="100" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B100" s="41">
         <v>90</v>
       </c>
@@ -5997,7 +6046,7 @@
       </c>
       <c r="P100" s="44"/>
     </row>
-    <row r="101" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B101" s="41">
         <v>91</v>
       </c>
@@ -6028,7 +6077,7 @@
       </c>
       <c r="P101" s="44"/>
     </row>
-    <row r="102" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="102" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B102" s="41">
         <v>92</v>
       </c>
@@ -6059,7 +6108,7 @@
       </c>
       <c r="P102" s="44"/>
     </row>
-    <row r="103" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="103" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B103" s="41">
         <v>93</v>
       </c>
@@ -6090,7 +6139,7 @@
       </c>
       <c r="P103" s="44"/>
     </row>
-    <row r="104" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="104" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B104" s="41">
         <v>94</v>
       </c>
@@ -6121,7 +6170,7 @@
       </c>
       <c r="P104" s="44"/>
     </row>
-    <row r="105" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="105" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B105" s="41">
         <v>95</v>
       </c>
@@ -6152,7 +6201,7 @@
       </c>
       <c r="P105" s="44"/>
     </row>
-    <row r="106" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="106" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B106" s="41">
         <v>96</v>
       </c>
@@ -6183,7 +6232,7 @@
       </c>
       <c r="P106" s="44"/>
     </row>
-    <row r="107" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B107" s="41">
         <v>97</v>
       </c>
@@ -6214,7 +6263,7 @@
       </c>
       <c r="P107" s="44"/>
     </row>
-    <row r="108" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="108" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B108" s="41">
         <v>98</v>
       </c>
@@ -6245,7 +6294,7 @@
       </c>
       <c r="P108" s="44"/>
     </row>
-    <row r="109" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B109" s="41">
         <v>99</v>
       </c>
@@ -6276,7 +6325,7 @@
       </c>
       <c r="P109" s="44"/>
     </row>
-    <row r="110" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="110" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B110" s="41">
         <v>100</v>
       </c>
@@ -6346,7 +6395,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xWindow="613" yWindow="898" count="5">
@@ -6395,49 +6444,49 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F28A4DB1-CB48-4778-AC73-C91746932E53}">
   <dimension ref="B2:P110"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.3046875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="15" width="18.69140625" customWidth="1"/>
-    <col min="16" max="16" width="64.53515625" customWidth="1"/>
+    <col min="3" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="64.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:16" x14ac:dyDescent="0.4">
-      <c r="C2" s="57" t="s">
-        <v>109</v>
-      </c>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="57"/>
-      <c r="L2" s="57"/>
-      <c r="M2" s="57"/>
-      <c r="N2" s="57"/>
-      <c r="O2" s="57"/>
-      <c r="P2" s="57"/>
-    </row>
-    <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C4" s="58" t="s">
+    <row r="2" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="C2" s="56" t="s">
+        <v>111</v>
+      </c>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="56"/>
+      <c r="M2" s="56"/>
+      <c r="N2" s="56"/>
+      <c r="O2" s="56"/>
+      <c r="P2" s="56"/>
+    </row>
+    <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C4" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="58"/>
-      <c r="L4" s="58"/>
-      <c r="M4" s="58"/>
-      <c r="N4" s="58"/>
-      <c r="O4" s="58"/>
-      <c r="P4" s="58"/>
-    </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="57"/>
+      <c r="L4" s="57"/>
+      <c r="M4" s="57"/>
+      <c r="N4" s="57"/>
+      <c r="O4" s="57"/>
+      <c r="P4" s="57"/>
+    </row>
+    <row r="5" spans="2:16" x14ac:dyDescent="0.25">
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
@@ -6453,8 +6502,8 @@
       <c r="O5" s="5"/>
       <c r="P5" s="5"/>
     </row>
-    <row r="6" spans="2:16" x14ac:dyDescent="0.4">
-      <c r="C6" s="55" t="s">
+    <row r="6" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="C6" s="58" t="s">
         <v>11</v>
       </c>
       <c r="D6" s="10" t="s">
@@ -6462,7 +6511,7 @@
       </c>
       <c r="E6" s="35">
         <f>SUM(N11:N110)</f>
-        <v>0</v>
+        <v>468.75</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
@@ -6476,18 +6525,18 @@
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
     </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.4">
-      <c r="C7" s="55"/>
+    <row r="7" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="C7" s="58"/>
       <c r="D7" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E7" s="36">
         <f>SUM(O11:O110)</f>
-        <v>0</v>
+        <v>687.42499999999995</v>
       </c>
       <c r="J7" s="37"/>
     </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B9" s="6"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -6495,22 +6544,22 @@
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
-      <c r="I9" s="56" t="s">
+      <c r="I9" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="J9" s="56"/>
+      <c r="J9" s="59"/>
       <c r="K9" s="7"/>
-      <c r="L9" s="56" t="s">
+      <c r="L9" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="M9" s="56"/>
-      <c r="N9" s="56" t="s">
+      <c r="M9" s="59"/>
+      <c r="N9" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="O9" s="56"/>
+      <c r="O9" s="59"/>
       <c r="P9" s="7"/>
     </row>
-    <row r="10" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="8" t="s">
         <v>17</v>
       </c>
@@ -6557,396 +6606,624 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="41">
         <v>1</v>
       </c>
       <c r="C11" s="42" t="str">
         <f>IF(ISBLANK(D11), "", _xlfn.CONCAT("T", TEXT(B11, "0000"), "/", VLOOKUP(D11, Internal!$B$35:C$39, 2, FALSE), IF(OR(D11="QA", D11="Revision"), _xlfn.CONCAT("/", H11), "")))</f>
-        <v/>
-      </c>
-      <c r="D11" s="44"/>
-      <c r="E11" s="43"/>
-      <c r="F11" s="43"/>
-      <c r="G11" s="44"/>
+        <v>T0001/M</v>
+      </c>
+      <c r="D11" s="55" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11" s="43" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" s="44" t="s">
+        <v>46</v>
+      </c>
       <c r="H11" s="43"/>
-      <c r="I11" s="46"/>
-      <c r="J11" s="46"/>
+      <c r="I11" s="46">
+        <v>46138.883333333331</v>
+      </c>
+      <c r="J11" s="46">
+        <v>46139.00277777778</v>
+      </c>
       <c r="K11" s="45" t="str">
         <f ca="1">IF(OR(I11="",J11=""),"",IF(AND(J11&lt;&gt;"",I11&gt;=NOW()),"Planned",IF(AND(J11&lt;&gt;"",J11&lt;NOW()),"Completed","Ongoing")))</f>
-        <v/>
-      </c>
-      <c r="L11" s="47"/>
-      <c r="M11" s="47"/>
-      <c r="N11" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L11" s="47">
+        <v>2.5</v>
+      </c>
+      <c r="M11" s="47">
+        <v>2.75</v>
+      </c>
+      <c r="N11" s="45">
         <f>IF(ISBLANK(L11), "", L11*VLOOKUP($F11,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O11" s="45" t="str">
+        <v>125</v>
+      </c>
+      <c r="O11" s="45">
         <f>IF(ISBLANK(M11), "", M11*VLOOKUP($F11,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P11" s="44"/>
-    </row>
-    <row r="12" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+        <v>137.5</v>
+      </c>
+      <c r="P11" s="44" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="12" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="41">
         <v>2</v>
       </c>
       <c r="C12" s="42" t="str">
         <f>IF(ISBLANK(D12), "", _xlfn.CONCAT("T", TEXT(B12, "0000"), "/", VLOOKUP(D12, Internal!$B$35:C$39, 2, FALSE), IF(OR(D12="QA", D12="Revision"), _xlfn.CONCAT("/", H12), "")))</f>
-        <v/>
-      </c>
-      <c r="D12" s="44"/>
-      <c r="E12" s="43"/>
-      <c r="F12" s="43"/>
-      <c r="G12" s="44"/>
+        <v>T0002/D</v>
+      </c>
+      <c r="D12" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="G12" s="44" t="s">
+        <v>48</v>
+      </c>
       <c r="H12" s="43"/>
-      <c r="I12" s="46"/>
-      <c r="J12" s="46"/>
+      <c r="I12" s="46">
+        <v>46139.361111111109</v>
+      </c>
+      <c r="J12" s="46">
+        <v>46139.37222222222</v>
+      </c>
       <c r="K12" s="45" t="str">
-        <f t="shared" ref="K12:K75" ca="1" si="0">IF(OR(I12="",J12=""),"",IF(AND(J12&lt;&gt;"",I12&gt;=NOW()),"Planned",IF(AND(J12&lt;&gt;"",J12&lt;NOW()),"Completed","Ongoing")))</f>
-        <v/>
-      </c>
-      <c r="L12" s="47"/>
-      <c r="M12" s="47"/>
-      <c r="N12" s="45" t="str">
+        <f ca="1">IF(OR(I12="",J12=""),"",IF(AND(J12&lt;&gt;"",I12&gt;=NOW()),"Planned",IF(AND(J12&lt;&gt;"",J12&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L12" s="47">
+        <v>0.5</v>
+      </c>
+      <c r="M12" s="47">
+        <v>0.26700000000000002</v>
+      </c>
+      <c r="N12" s="45">
         <f>IF(ISBLANK(L12), "", L12*VLOOKUP($F12,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O12" s="45" t="str">
+        <v>12.5</v>
+      </c>
+      <c r="O12" s="45">
         <f>IF(ISBLANK(M12), "", M12*VLOOKUP($F12,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P12" s="44"/>
-    </row>
-    <row r="13" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+        <v>6.6750000000000007</v>
+      </c>
+      <c r="P12" s="44" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="13" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="41">
         <v>3</v>
       </c>
       <c r="C13" s="42" t="str">
         <f>IF(ISBLANK(D13), "", _xlfn.CONCAT("T", TEXT(B13, "0000"), "/", VLOOKUP(D13, Internal!$B$35:C$39, 2, FALSE), IF(OR(D13="QA", D13="Revision"), _xlfn.CONCAT("/", H13), "")))</f>
-        <v/>
-      </c>
-      <c r="D13" s="44"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="43"/>
-      <c r="G13" s="44"/>
+        <v>T0003/D</v>
+      </c>
+      <c r="D13" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="43" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="G13" s="44" t="s">
+        <v>48</v>
+      </c>
       <c r="H13" s="43"/>
-      <c r="I13" s="46"/>
-      <c r="J13" s="46"/>
+      <c r="I13" s="46">
+        <v>46140.62222222222</v>
+      </c>
+      <c r="J13" s="46">
+        <v>46140.668055555558</v>
+      </c>
       <c r="K13" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L13" s="47"/>
-      <c r="M13" s="47"/>
-      <c r="N13" s="45" t="str">
+        <f t="shared" ref="K13:K75" ca="1" si="0">IF(OR(I13="",J13=""),"",IF(AND(J13&lt;&gt;"",I13&gt;=NOW()),"Planned",IF(AND(J13&lt;&gt;"",J13&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L13" s="47">
+        <v>1</v>
+      </c>
+      <c r="M13" s="47">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="N13" s="45">
         <f>IF(ISBLANK(L13), "", L13*VLOOKUP($F13,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O13" s="45" t="str">
+        <v>25</v>
+      </c>
+      <c r="O13" s="45">
         <f>IF(ISBLANK(M13), "", M13*VLOOKUP($F13,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P13" s="44"/>
-    </row>
-    <row r="14" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+        <v>27.500000000000004</v>
+      </c>
+      <c r="P13" s="44" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="14" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="41">
         <v>4</v>
       </c>
       <c r="C14" s="42" t="str">
         <f>IF(ISBLANK(D14), "", _xlfn.CONCAT("T", TEXT(B14, "0000"), "/", VLOOKUP(D14, Internal!$B$35:C$39, 2, FALSE), IF(OR(D14="QA", D14="Revision"), _xlfn.CONCAT("/", H14), "")))</f>
-        <v/>
-      </c>
-      <c r="D14" s="44"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="43"/>
-      <c r="G14" s="44"/>
+        <v>T0004/D</v>
+      </c>
+      <c r="D14" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="F14" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="G14" s="44" t="s">
+        <v>48</v>
+      </c>
       <c r="H14" s="43"/>
-      <c r="I14" s="46"/>
-      <c r="J14" s="46"/>
+      <c r="I14" s="46">
+        <v>46139.368055555555</v>
+      </c>
+      <c r="J14" s="46">
+        <v>46139.395833333336</v>
+      </c>
       <c r="K14" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L14" s="47"/>
-      <c r="M14" s="47"/>
-      <c r="N14" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L14" s="47">
+        <v>0.5</v>
+      </c>
+      <c r="M14" s="47">
+        <v>0.66</v>
+      </c>
+      <c r="N14" s="45">
         <f>IF(ISBLANK(L14), "", L14*VLOOKUP($F14,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O14" s="45" t="str">
+        <v>12.5</v>
+      </c>
+      <c r="O14" s="45">
         <f>IF(ISBLANK(M14), "", M14*VLOOKUP($F14,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P14" s="44"/>
-    </row>
-    <row r="15" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+        <v>16.5</v>
+      </c>
+      <c r="P14" s="44" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="15" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="41">
         <v>5</v>
       </c>
       <c r="C15" s="42" t="str">
         <f>IF(ISBLANK(D15), "", _xlfn.CONCAT("T", TEXT(B15, "0000"), "/", VLOOKUP(D15, Internal!$B$35:C$39, 2, FALSE), IF(OR(D15="QA", D15="Revision"), _xlfn.CONCAT("/", H15), "")))</f>
-        <v/>
-      </c>
-      <c r="D15" s="44"/>
-      <c r="E15" s="43"/>
-      <c r="F15" s="43"/>
-      <c r="G15" s="44"/>
+        <v>T0005/D</v>
+      </c>
+      <c r="D15" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" s="43" t="s">
+        <v>58</v>
+      </c>
+      <c r="F15" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="G15" s="44" t="s">
+        <v>48</v>
+      </c>
       <c r="H15" s="43"/>
-      <c r="I15" s="46"/>
-      <c r="J15" s="46"/>
+      <c r="I15" s="46">
+        <v>46148.818055555559</v>
+      </c>
+      <c r="J15" s="46">
+        <v>46149.993750000001</v>
+      </c>
       <c r="K15" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L15" s="47"/>
-      <c r="M15" s="47"/>
-      <c r="N15" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L15" s="47">
+        <v>2</v>
+      </c>
+      <c r="M15" s="47">
+        <v>4</v>
+      </c>
+      <c r="N15" s="45">
         <f>IF(ISBLANK(L15), "", L15*VLOOKUP($F15,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O15" s="45" t="str">
+        <v>50</v>
+      </c>
+      <c r="O15" s="45">
         <f>IF(ISBLANK(M15), "", M15*VLOOKUP($F15,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P15" s="44"/>
-    </row>
-    <row r="16" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+        <v>100</v>
+      </c>
+      <c r="P15" s="44" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="16" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="41">
         <v>6</v>
       </c>
       <c r="C16" s="42" t="str">
         <f>IF(ISBLANK(D16), "", _xlfn.CONCAT("T", TEXT(B16, "0000"), "/", VLOOKUP(D16, Internal!$B$35:C$39, 2, FALSE), IF(OR(D16="QA", D16="Revision"), _xlfn.CONCAT("/", H16), "")))</f>
-        <v/>
-      </c>
-      <c r="D16" s="44"/>
-      <c r="E16" s="43"/>
-      <c r="F16" s="43"/>
-      <c r="G16" s="44"/>
+        <v>T0006/D</v>
+      </c>
+      <c r="D16" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" s="43" t="s">
+        <v>61</v>
+      </c>
+      <c r="F16" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="G16" s="44" t="s">
+        <v>48</v>
+      </c>
       <c r="H16" s="43"/>
-      <c r="I16" s="46"/>
-      <c r="J16" s="46"/>
+      <c r="I16" s="46">
+        <v>46149.444444444445</v>
+      </c>
+      <c r="J16" s="46">
+        <v>46149.492361111108</v>
+      </c>
       <c r="K16" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L16" s="47"/>
-      <c r="M16" s="47"/>
-      <c r="N16" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L16" s="47">
+        <v>1</v>
+      </c>
+      <c r="M16" s="47">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="N16" s="45">
         <f>IF(ISBLANK(L16), "", L16*VLOOKUP($F16,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O16" s="45" t="str">
+        <v>25</v>
+      </c>
+      <c r="O16" s="45">
         <f>IF(ISBLANK(M16), "", M16*VLOOKUP($F16,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P16" s="44"/>
-    </row>
-    <row r="17" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+        <v>28.749999999999996</v>
+      </c>
+      <c r="P16" s="44" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="17" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="41">
         <v>7</v>
       </c>
       <c r="C17" s="42" t="str">
         <f>IF(ISBLANK(D17), "", _xlfn.CONCAT("T", TEXT(B17, "0000"), "/", VLOOKUP(D17, Internal!$B$35:C$39, 2, FALSE), IF(OR(D17="QA", D17="Revision"), _xlfn.CONCAT("/", H17), "")))</f>
-        <v/>
-      </c>
-      <c r="D17" s="44"/>
-      <c r="E17" s="43"/>
-      <c r="F17" s="43"/>
-      <c r="G17" s="44"/>
+        <v>T0007/D</v>
+      </c>
+      <c r="D17" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="E17" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="F17" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="G17" s="44" t="s">
+        <v>48</v>
+      </c>
       <c r="H17" s="43"/>
-      <c r="I17" s="46"/>
-      <c r="J17" s="46"/>
+      <c r="I17" s="46">
+        <v>46139.8125</v>
+      </c>
+      <c r="J17" s="46">
+        <v>46147.560416666667</v>
+      </c>
       <c r="K17" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L17" s="47"/>
-      <c r="M17" s="47"/>
-      <c r="N17" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L17" s="47">
+        <v>1</v>
+      </c>
+      <c r="M17" s="47">
+        <v>3</v>
+      </c>
+      <c r="N17" s="45">
         <f>IF(ISBLANK(L17), "", L17*VLOOKUP($F17,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O17" s="45" t="str">
+        <v>25</v>
+      </c>
+      <c r="O17" s="45">
         <f>IF(ISBLANK(M17), "", M17*VLOOKUP($F17,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P17" s="44"/>
-    </row>
-    <row r="18" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+        <v>75</v>
+      </c>
+      <c r="P17" s="44" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="18" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="41">
         <v>8</v>
       </c>
       <c r="C18" s="42" t="str">
         <f>IF(ISBLANK(D18), "", _xlfn.CONCAT("T", TEXT(B18, "0000"), "/", VLOOKUP(D18, Internal!$B$35:C$39, 2, FALSE), IF(OR(D18="QA", D18="Revision"), _xlfn.CONCAT("/", H18), "")))</f>
-        <v/>
-      </c>
-      <c r="D18" s="44"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="43"/>
-      <c r="G18" s="44"/>
+        <v>T0008/D</v>
+      </c>
+      <c r="D18" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="E18" s="43" t="s">
+        <v>53</v>
+      </c>
+      <c r="F18" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="G18" s="44" t="s">
+        <v>48</v>
+      </c>
       <c r="H18" s="43"/>
-      <c r="I18" s="46"/>
-      <c r="J18" s="46"/>
+      <c r="I18" s="46">
+        <v>46150.581944444442</v>
+      </c>
+      <c r="J18" s="46">
+        <v>46150.708333333336</v>
+      </c>
       <c r="K18" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L18" s="47"/>
-      <c r="M18" s="47"/>
-      <c r="N18" s="45" t="str">
+        <f ca="1">IF(OR(I18="",J18=""),"",IF(AND(J18&lt;&gt;"",I18&gt;=NOW()),"Planned",IF(AND(J18&lt;&gt;"",J18&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L18" s="47">
+        <v>1</v>
+      </c>
+      <c r="M18" s="47">
+        <v>3.04</v>
+      </c>
+      <c r="N18" s="45">
         <f>IF(ISBLANK(L18), "", L18*VLOOKUP($F18,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O18" s="45" t="str">
+        <v>25</v>
+      </c>
+      <c r="O18" s="45">
         <f>IF(ISBLANK(M18), "", M18*VLOOKUP($F18,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P18" s="44"/>
-    </row>
-    <row r="19" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+        <v>76</v>
+      </c>
+      <c r="P18" s="44" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="19" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="41">
         <v>9</v>
       </c>
       <c r="C19" s="42" t="str">
         <f>IF(ISBLANK(D19), "", _xlfn.CONCAT("T", TEXT(B19, "0000"), "/", VLOOKUP(D19, Internal!$B$35:C$39, 2, FALSE), IF(OR(D19="QA", D19="Revision"), _xlfn.CONCAT("/", H19), "")))</f>
-        <v/>
-      </c>
-      <c r="D19" s="44"/>
-      <c r="E19" s="43"/>
-      <c r="F19" s="43"/>
-      <c r="G19" s="44"/>
+        <v>T0009/D</v>
+      </c>
+      <c r="D19" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="E19" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="F19" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="G19" s="44" t="s">
+        <v>48</v>
+      </c>
       <c r="H19" s="43"/>
-      <c r="I19" s="46"/>
-      <c r="J19" s="46"/>
+      <c r="I19" s="46">
+        <v>46145.988194444442</v>
+      </c>
+      <c r="J19" s="46">
+        <v>46146.008333333331</v>
+      </c>
       <c r="K19" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L19" s="47"/>
-      <c r="M19" s="47"/>
-      <c r="N19" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L19" s="47">
+        <v>1</v>
+      </c>
+      <c r="M19" s="47">
+        <v>0.5</v>
+      </c>
+      <c r="N19" s="45">
         <f>IF(ISBLANK(L19), "", L19*VLOOKUP($F19,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O19" s="45" t="str">
+        <v>25</v>
+      </c>
+      <c r="O19" s="45">
         <f>IF(ISBLANK(M19), "", M19*VLOOKUP($F19,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P19" s="44"/>
-    </row>
-    <row r="20" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+        <v>12.5</v>
+      </c>
+      <c r="P19" s="44" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="20" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="41">
         <v>10</v>
       </c>
       <c r="C20" s="42" t="str">
         <f>IF(ISBLANK(D20), "", _xlfn.CONCAT("T", TEXT(B20, "0000"), "/", VLOOKUP(D20, Internal!$B$35:C$39, 2, FALSE), IF(OR(D20="QA", D20="Revision"), _xlfn.CONCAT("/", H20), "")))</f>
-        <v/>
-      </c>
-      <c r="D20" s="44"/>
-      <c r="E20" s="43"/>
-      <c r="F20" s="43"/>
-      <c r="G20" s="44"/>
+        <v>T0010/D</v>
+      </c>
+      <c r="D20" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="E20" s="43" t="s">
+        <v>61</v>
+      </c>
+      <c r="F20" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="G20" s="44" t="s">
+        <v>48</v>
+      </c>
       <c r="H20" s="43"/>
-      <c r="I20" s="46"/>
-      <c r="J20" s="46"/>
+      <c r="I20" s="46">
+        <v>46147.683333333334</v>
+      </c>
+      <c r="J20" s="46">
+        <v>46147.757638888892</v>
+      </c>
       <c r="K20" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L20" s="47"/>
-      <c r="M20" s="47"/>
-      <c r="N20" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L20" s="47">
+        <v>1.5</v>
+      </c>
+      <c r="M20" s="47">
+        <v>1.78</v>
+      </c>
+      <c r="N20" s="45">
         <f>IF(ISBLANK(L20), "", L20*VLOOKUP($F20,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O20" s="45" t="str">
+        <v>37.5</v>
+      </c>
+      <c r="O20" s="45">
         <f>IF(ISBLANK(M20), "", M20*VLOOKUP($F20,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P20" s="44"/>
-    </row>
-    <row r="21" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+        <v>44.5</v>
+      </c>
+      <c r="P20" s="44" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="21" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="41">
         <v>11</v>
       </c>
       <c r="C21" s="42" t="str">
         <f>IF(ISBLANK(D21), "", _xlfn.CONCAT("T", TEXT(B21, "0000"), "/", VLOOKUP(D21, Internal!$B$35:C$39, 2, FALSE), IF(OR(D21="QA", D21="Revision"), _xlfn.CONCAT("/", H21), "")))</f>
-        <v/>
-      </c>
-      <c r="D21" s="44"/>
-      <c r="E21" s="43"/>
-      <c r="F21" s="43"/>
-      <c r="G21" s="44"/>
+        <v>T0011/D</v>
+      </c>
+      <c r="D21" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="E21" s="43" t="s">
+        <v>58</v>
+      </c>
+      <c r="F21" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="G21" s="44" t="s">
+        <v>48</v>
+      </c>
       <c r="H21" s="43"/>
-      <c r="I21" s="46"/>
-      <c r="J21" s="46"/>
+      <c r="I21" s="46">
+        <v>46146.363194444442</v>
+      </c>
+      <c r="J21" s="46">
+        <v>46148.818055555559</v>
+      </c>
       <c r="K21" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L21" s="47"/>
-      <c r="M21" s="47"/>
-      <c r="N21" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L21" s="47">
+        <v>1</v>
+      </c>
+      <c r="M21" s="47">
+        <v>2.5</v>
+      </c>
+      <c r="N21" s="45">
         <f>IF(ISBLANK(L21), "", L21*VLOOKUP($F21,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O21" s="45" t="str">
+        <v>25</v>
+      </c>
+      <c r="O21" s="45">
         <f>IF(ISBLANK(M21), "", M21*VLOOKUP($F21,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P21" s="44"/>
-    </row>
-    <row r="22" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+        <v>62.5</v>
+      </c>
+      <c r="P21" s="44" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="22" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="41">
         <v>12</v>
       </c>
       <c r="C22" s="42" t="str">
         <f>IF(ISBLANK(D22), "", _xlfn.CONCAT("T", TEXT(B22, "0000"), "/", VLOOKUP(D22, Internal!$B$35:C$39, 2, FALSE), IF(OR(D22="QA", D22="Revision"), _xlfn.CONCAT("/", H22), "")))</f>
-        <v/>
-      </c>
-      <c r="D22" s="44"/>
-      <c r="E22" s="43"/>
-      <c r="F22" s="43"/>
-      <c r="G22" s="44"/>
+        <v>T0012/D</v>
+      </c>
+      <c r="D22" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="E22" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="F22" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="G22" s="44" t="s">
+        <v>102</v>
+      </c>
       <c r="H22" s="43"/>
-      <c r="I22" s="46"/>
-      <c r="J22" s="46"/>
+      <c r="I22" s="46">
+        <v>46146.361805555556</v>
+      </c>
+      <c r="J22" s="46">
+        <v>46146.399305555555</v>
+      </c>
       <c r="K22" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L22" s="47"/>
-      <c r="M22" s="47"/>
-      <c r="N22" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L22" s="47">
+        <v>1</v>
+      </c>
+      <c r="M22" s="47">
+        <v>1</v>
+      </c>
+      <c r="N22" s="45">
         <f>IF(ISBLANK(L22), "", L22*VLOOKUP($F22,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O22" s="45" t="str">
+        <v>25</v>
+      </c>
+      <c r="O22" s="45">
         <f>IF(ISBLANK(M22), "", M22*VLOOKUP($F22,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P22" s="44"/>
-    </row>
-    <row r="23" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+      <c r="P22" s="44" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="23" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B23" s="41">
         <v>13</v>
       </c>
       <c r="C23" s="42" t="str">
         <f>IF(ISBLANK(D23), "", _xlfn.CONCAT("T", TEXT(B23, "0000"), "/", VLOOKUP(D23, Internal!$B$35:C$39, 2, FALSE), IF(OR(D23="QA", D23="Revision"), _xlfn.CONCAT("/", H23), "")))</f>
-        <v/>
-      </c>
-      <c r="D23" s="44"/>
-      <c r="E23" s="43"/>
-      <c r="F23" s="43"/>
-      <c r="G23" s="44"/>
+        <v>T0013/D</v>
+      </c>
+      <c r="D23" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="E23" s="43" t="s">
+        <v>53</v>
+      </c>
+      <c r="F23" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="G23" s="44" t="s">
+        <v>102</v>
+      </c>
       <c r="H23" s="43"/>
-      <c r="I23" s="46"/>
-      <c r="J23" s="46"/>
+      <c r="I23" s="46">
+        <v>46146.362500000003</v>
+      </c>
+      <c r="J23" s="46">
+        <v>46146.402777777781</v>
+      </c>
       <c r="K23" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
+        <v>Completed</v>
       </c>
       <c r="L23" s="47"/>
       <c r="M23" s="47"/>
@@ -6958,102 +7235,158 @@
         <f>IF(ISBLANK(M23), "", M23*VLOOKUP($F23,Internal!$B$26:$C$32,2,FALSE))</f>
         <v/>
       </c>
-      <c r="P23" s="44"/>
-    </row>
-    <row r="24" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="P23" s="44" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="24" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="41">
         <v>14</v>
       </c>
       <c r="C24" s="42" t="str">
         <f>IF(ISBLANK(D24), "", _xlfn.CONCAT("T", TEXT(B24, "0000"), "/", VLOOKUP(D24, Internal!$B$35:C$39, 2, FALSE), IF(OR(D24="QA", D24="Revision"), _xlfn.CONCAT("/", H24), "")))</f>
-        <v/>
-      </c>
-      <c r="D24" s="44"/>
-      <c r="E24" s="43"/>
-      <c r="F24" s="43"/>
-      <c r="G24" s="44"/>
+        <v>T0014/D</v>
+      </c>
+      <c r="D24" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="E24" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="F24" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="G24" s="44" t="s">
+        <v>102</v>
+      </c>
       <c r="H24" s="43"/>
-      <c r="I24" s="46"/>
-      <c r="J24" s="46"/>
+      <c r="I24" s="46">
+        <v>46147.442361111112</v>
+      </c>
+      <c r="J24" s="46">
+        <v>46147.505555555559</v>
+      </c>
       <c r="K24" s="45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L24" s="47"/>
-      <c r="M24" s="47"/>
-      <c r="N24" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L24" s="47">
+        <v>0.25</v>
+      </c>
+      <c r="M24" s="47">
+        <v>1.5</v>
+      </c>
+      <c r="N24" s="45">
         <f>IF(ISBLANK(L24), "", L24*VLOOKUP($F24,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O24" s="45" t="str">
+        <v>6.25</v>
+      </c>
+      <c r="O24" s="45">
         <f>IF(ISBLANK(M24), "", M24*VLOOKUP($F24,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P24" s="44"/>
-    </row>
-    <row r="25" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+        <v>37.5</v>
+      </c>
+      <c r="P24" s="44" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="25" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B25" s="41">
         <v>15</v>
       </c>
       <c r="C25" s="42" t="str">
         <f>IF(ISBLANK(D25), "", _xlfn.CONCAT("T", TEXT(B25, "0000"), "/", VLOOKUP(D25, Internal!$B$35:C$39, 2, FALSE), IF(OR(D25="QA", D25="Revision"), _xlfn.CONCAT("/", H25), "")))</f>
-        <v/>
-      </c>
-      <c r="D25" s="44"/>
-      <c r="E25" s="43"/>
-      <c r="F25" s="43"/>
-      <c r="G25" s="44"/>
+        <v>T0015/D</v>
+      </c>
+      <c r="D25" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="E25" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="F25" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="G25" s="44" t="s">
+        <v>102</v>
+      </c>
       <c r="H25" s="43"/>
-      <c r="I25" s="46"/>
-      <c r="J25" s="46"/>
+      <c r="I25" s="46">
+        <v>46146.399305555555</v>
+      </c>
+      <c r="J25" s="46">
+        <v>46146.444444444445</v>
+      </c>
       <c r="K25" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L25" s="47"/>
-      <c r="M25" s="47"/>
-      <c r="N25" s="45" t="str">
+        <f ca="1">IF(OR(I25="",J25=""),"",IF(AND(J25&lt;&gt;"",I25&gt;=NOW()),"Planned",IF(AND(J25&lt;&gt;"",J25&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L25" s="47">
+        <v>1</v>
+      </c>
+      <c r="M25" s="47">
+        <v>1</v>
+      </c>
+      <c r="N25" s="45">
         <f>IF(ISBLANK(L25), "", L25*VLOOKUP($F25,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O25" s="45" t="str">
+        <v>25</v>
+      </c>
+      <c r="O25" s="45">
         <f>IF(ISBLANK(M25), "", M25*VLOOKUP($F25,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P25" s="44"/>
-    </row>
-    <row r="26" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+      <c r="P25" s="44" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="26" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="41">
         <v>16</v>
       </c>
       <c r="C26" s="42" t="str">
         <f>IF(ISBLANK(D26), "", _xlfn.CONCAT("T", TEXT(B26, "0000"), "/", VLOOKUP(D26, Internal!$B$35:C$39, 2, FALSE), IF(OR(D26="QA", D26="Revision"), _xlfn.CONCAT("/", H26), "")))</f>
-        <v/>
-      </c>
-      <c r="D26" s="44"/>
-      <c r="E26" s="43"/>
-      <c r="F26" s="43"/>
-      <c r="G26" s="44"/>
+        <v>T0016/D</v>
+      </c>
+      <c r="D26" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="E26" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="F26" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="G26" s="44" t="s">
+        <v>48</v>
+      </c>
       <c r="H26" s="43"/>
-      <c r="I26" s="46"/>
-      <c r="J26" s="46"/>
+      <c r="I26" s="46">
+        <v>46148.402777777781</v>
+      </c>
+      <c r="J26" s="46">
+        <v>46148.424305555556</v>
+      </c>
       <c r="K26" s="45" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L26" s="47"/>
-      <c r="M26" s="47"/>
-      <c r="N26" s="45" t="str">
+        <f ca="1">IF(OR(I26="",J26=""),"",IF(AND(J26&lt;&gt;"",I26&gt;=NOW()),"Planned",IF(AND(J26&lt;&gt;"",J26&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L26" s="47">
+        <v>1</v>
+      </c>
+      <c r="M26" s="47">
+        <v>0.5</v>
+      </c>
+      <c r="N26" s="45">
         <f>IF(ISBLANK(L26), "", L26*VLOOKUP($F26,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O26" s="45" t="str">
+        <v>25</v>
+      </c>
+      <c r="O26" s="45">
         <f>IF(ISBLANK(M26), "", M26*VLOOKUP($F26,Internal!$B$26:$C$32,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P26" s="44"/>
-    </row>
-    <row r="27" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+        <v>12.5</v>
+      </c>
+      <c r="P26" s="44" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="27" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B27" s="41">
         <v>17</v>
       </c>
@@ -7084,7 +7417,7 @@
       </c>
       <c r="P27" s="44"/>
     </row>
-    <row r="28" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B28" s="41">
         <v>18</v>
       </c>
@@ -7115,7 +7448,7 @@
       </c>
       <c r="P28" s="44"/>
     </row>
-    <row r="29" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B29" s="41">
         <v>19</v>
       </c>
@@ -7146,7 +7479,7 @@
       </c>
       <c r="P29" s="44"/>
     </row>
-    <row r="30" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="41">
         <v>20</v>
       </c>
@@ -7177,7 +7510,7 @@
       </c>
       <c r="P30" s="44"/>
     </row>
-    <row r="31" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B31" s="41">
         <v>21</v>
       </c>
@@ -7208,7 +7541,7 @@
       </c>
       <c r="P31" s="44"/>
     </row>
-    <row r="32" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B32" s="41">
         <v>22</v>
       </c>
@@ -7239,7 +7572,7 @@
       </c>
       <c r="P32" s="44"/>
     </row>
-    <row r="33" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="41">
         <v>23</v>
       </c>
@@ -7270,7 +7603,7 @@
       </c>
       <c r="P33" s="44"/>
     </row>
-    <row r="34" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B34" s="41">
         <v>24</v>
       </c>
@@ -7301,7 +7634,7 @@
       </c>
       <c r="P34" s="44"/>
     </row>
-    <row r="35" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B35" s="41">
         <v>25</v>
       </c>
@@ -7332,7 +7665,7 @@
       </c>
       <c r="P35" s="44"/>
     </row>
-    <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="41">
         <v>26</v>
       </c>
@@ -7363,7 +7696,7 @@
       </c>
       <c r="P36" s="44"/>
     </row>
-    <row r="37" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="41">
         <v>27</v>
       </c>
@@ -7394,7 +7727,7 @@
       </c>
       <c r="P37" s="44"/>
     </row>
-    <row r="38" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B38" s="41">
         <v>28</v>
       </c>
@@ -7425,7 +7758,7 @@
       </c>
       <c r="P38" s="44"/>
     </row>
-    <row r="39" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B39" s="41">
         <v>29</v>
       </c>
@@ -7456,7 +7789,7 @@
       </c>
       <c r="P39" s="44"/>
     </row>
-    <row r="40" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B40" s="41">
         <v>30</v>
       </c>
@@ -7487,7 +7820,7 @@
       </c>
       <c r="P40" s="44"/>
     </row>
-    <row r="41" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B41" s="41">
         <v>31</v>
       </c>
@@ -7518,7 +7851,7 @@
       </c>
       <c r="P41" s="44"/>
     </row>
-    <row r="42" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B42" s="41">
         <v>32</v>
       </c>
@@ -7549,7 +7882,7 @@
       </c>
       <c r="P42" s="44"/>
     </row>
-    <row r="43" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B43" s="41">
         <v>33</v>
       </c>
@@ -7580,7 +7913,7 @@
       </c>
       <c r="P43" s="44"/>
     </row>
-    <row r="44" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B44" s="41">
         <v>34</v>
       </c>
@@ -7611,7 +7944,7 @@
       </c>
       <c r="P44" s="44"/>
     </row>
-    <row r="45" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B45" s="41">
         <v>35</v>
       </c>
@@ -7642,7 +7975,7 @@
       </c>
       <c r="P45" s="44"/>
     </row>
-    <row r="46" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B46" s="41">
         <v>36</v>
       </c>
@@ -7673,7 +8006,7 @@
       </c>
       <c r="P46" s="44"/>
     </row>
-    <row r="47" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B47" s="41">
         <v>37</v>
       </c>
@@ -7704,7 +8037,7 @@
       </c>
       <c r="P47" s="44"/>
     </row>
-    <row r="48" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B48" s="41">
         <v>38</v>
       </c>
@@ -7735,7 +8068,7 @@
       </c>
       <c r="P48" s="44"/>
     </row>
-    <row r="49" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B49" s="41">
         <v>39</v>
       </c>
@@ -7766,7 +8099,7 @@
       </c>
       <c r="P49" s="44"/>
     </row>
-    <row r="50" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B50" s="41">
         <v>40</v>
       </c>
@@ -7797,7 +8130,7 @@
       </c>
       <c r="P50" s="44"/>
     </row>
-    <row r="51" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B51" s="41">
         <v>41</v>
       </c>
@@ -7828,7 +8161,7 @@
       </c>
       <c r="P51" s="44"/>
     </row>
-    <row r="52" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B52" s="41">
         <v>42</v>
       </c>
@@ -7859,7 +8192,7 @@
       </c>
       <c r="P52" s="44"/>
     </row>
-    <row r="53" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B53" s="41">
         <v>43</v>
       </c>
@@ -7890,7 +8223,7 @@
       </c>
       <c r="P53" s="44"/>
     </row>
-    <row r="54" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B54" s="41">
         <v>44</v>
       </c>
@@ -7921,7 +8254,7 @@
       </c>
       <c r="P54" s="44"/>
     </row>
-    <row r="55" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="55" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B55" s="41">
         <v>45</v>
       </c>
@@ -7952,7 +8285,7 @@
       </c>
       <c r="P55" s="44"/>
     </row>
-    <row r="56" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B56" s="41">
         <v>46</v>
       </c>
@@ -7983,7 +8316,7 @@
       </c>
       <c r="P56" s="44"/>
     </row>
-    <row r="57" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B57" s="41">
         <v>47</v>
       </c>
@@ -8014,7 +8347,7 @@
       </c>
       <c r="P57" s="44"/>
     </row>
-    <row r="58" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B58" s="41">
         <v>48</v>
       </c>
@@ -8045,7 +8378,7 @@
       </c>
       <c r="P58" s="44"/>
     </row>
-    <row r="59" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B59" s="41">
         <v>49</v>
       </c>
@@ -8076,7 +8409,7 @@
       </c>
       <c r="P59" s="44"/>
     </row>
-    <row r="60" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B60" s="41">
         <v>50</v>
       </c>
@@ -8107,7 +8440,7 @@
       </c>
       <c r="P60" s="44"/>
     </row>
-    <row r="61" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B61" s="41">
         <v>51</v>
       </c>
@@ -8138,7 +8471,7 @@
       </c>
       <c r="P61" s="44"/>
     </row>
-    <row r="62" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B62" s="41">
         <v>52</v>
       </c>
@@ -8169,7 +8502,7 @@
       </c>
       <c r="P62" s="44"/>
     </row>
-    <row r="63" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B63" s="41">
         <v>53</v>
       </c>
@@ -8200,7 +8533,7 @@
       </c>
       <c r="P63" s="44"/>
     </row>
-    <row r="64" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B64" s="41">
         <v>54</v>
       </c>
@@ -8231,7 +8564,7 @@
       </c>
       <c r="P64" s="44"/>
     </row>
-    <row r="65" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B65" s="41">
         <v>55</v>
       </c>
@@ -8262,7 +8595,7 @@
       </c>
       <c r="P65" s="44"/>
     </row>
-    <row r="66" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B66" s="41">
         <v>56</v>
       </c>
@@ -8293,7 +8626,7 @@
       </c>
       <c r="P66" s="44"/>
     </row>
-    <row r="67" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B67" s="41">
         <v>57</v>
       </c>
@@ -8324,7 +8657,7 @@
       </c>
       <c r="P67" s="44"/>
     </row>
-    <row r="68" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B68" s="41">
         <v>58</v>
       </c>
@@ -8355,7 +8688,7 @@
       </c>
       <c r="P68" s="44"/>
     </row>
-    <row r="69" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B69" s="41">
         <v>59</v>
       </c>
@@ -8386,7 +8719,7 @@
       </c>
       <c r="P69" s="44"/>
     </row>
-    <row r="70" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B70" s="41">
         <v>60</v>
       </c>
@@ -8417,7 +8750,7 @@
       </c>
       <c r="P70" s="44"/>
     </row>
-    <row r="71" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B71" s="41">
         <v>61</v>
       </c>
@@ -8448,7 +8781,7 @@
       </c>
       <c r="P71" s="44"/>
     </row>
-    <row r="72" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B72" s="41">
         <v>62</v>
       </c>
@@ -8479,7 +8812,7 @@
       </c>
       <c r="P72" s="44"/>
     </row>
-    <row r="73" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B73" s="41">
         <v>63</v>
       </c>
@@ -8510,7 +8843,7 @@
       </c>
       <c r="P73" s="44"/>
     </row>
-    <row r="74" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B74" s="41">
         <v>64</v>
       </c>
@@ -8541,7 +8874,7 @@
       </c>
       <c r="P74" s="44"/>
     </row>
-    <row r="75" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B75" s="41">
         <v>65</v>
       </c>
@@ -8572,7 +8905,7 @@
       </c>
       <c r="P75" s="44"/>
     </row>
-    <row r="76" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B76" s="41">
         <v>66</v>
       </c>
@@ -8603,7 +8936,7 @@
       </c>
       <c r="P76" s="44"/>
     </row>
-    <row r="77" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B77" s="41">
         <v>67</v>
       </c>
@@ -8634,7 +8967,7 @@
       </c>
       <c r="P77" s="44"/>
     </row>
-    <row r="78" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B78" s="41">
         <v>68</v>
       </c>
@@ -8665,7 +8998,7 @@
       </c>
       <c r="P78" s="44"/>
     </row>
-    <row r="79" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B79" s="41">
         <v>69</v>
       </c>
@@ -8696,7 +9029,7 @@
       </c>
       <c r="P79" s="44"/>
     </row>
-    <row r="80" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B80" s="41">
         <v>70</v>
       </c>
@@ -8727,7 +9060,7 @@
       </c>
       <c r="P80" s="44"/>
     </row>
-    <row r="81" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B81" s="41">
         <v>71</v>
       </c>
@@ -8758,7 +9091,7 @@
       </c>
       <c r="P81" s="44"/>
     </row>
-    <row r="82" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B82" s="41">
         <v>72</v>
       </c>
@@ -8789,7 +9122,7 @@
       </c>
       <c r="P82" s="44"/>
     </row>
-    <row r="83" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B83" s="41">
         <v>73</v>
       </c>
@@ -8820,7 +9153,7 @@
       </c>
       <c r="P83" s="44"/>
     </row>
-    <row r="84" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B84" s="41">
         <v>74</v>
       </c>
@@ -8851,7 +9184,7 @@
       </c>
       <c r="P84" s="44"/>
     </row>
-    <row r="85" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B85" s="41">
         <v>75</v>
       </c>
@@ -8882,7 +9215,7 @@
       </c>
       <c r="P85" s="44"/>
     </row>
-    <row r="86" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B86" s="41">
         <v>76</v>
       </c>
@@ -8913,7 +9246,7 @@
       </c>
       <c r="P86" s="44"/>
     </row>
-    <row r="87" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B87" s="41">
         <v>77</v>
       </c>
@@ -8944,7 +9277,7 @@
       </c>
       <c r="P87" s="44"/>
     </row>
-    <row r="88" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B88" s="41">
         <v>78</v>
       </c>
@@ -8975,7 +9308,7 @@
       </c>
       <c r="P88" s="44"/>
     </row>
-    <row r="89" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B89" s="41">
         <v>79</v>
       </c>
@@ -9006,7 +9339,7 @@
       </c>
       <c r="P89" s="44"/>
     </row>
-    <row r="90" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B90" s="41">
         <v>80</v>
       </c>
@@ -9037,7 +9370,7 @@
       </c>
       <c r="P90" s="44"/>
     </row>
-    <row r="91" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="91" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B91" s="41">
         <v>81</v>
       </c>
@@ -9068,7 +9401,7 @@
       </c>
       <c r="P91" s="44"/>
     </row>
-    <row r="92" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B92" s="41">
         <v>82</v>
       </c>
@@ -9099,7 +9432,7 @@
       </c>
       <c r="P92" s="44"/>
     </row>
-    <row r="93" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="93" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B93" s="41">
         <v>83</v>
       </c>
@@ -9130,7 +9463,7 @@
       </c>
       <c r="P93" s="44"/>
     </row>
-    <row r="94" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B94" s="41">
         <v>84</v>
       </c>
@@ -9161,7 +9494,7 @@
       </c>
       <c r="P94" s="44"/>
     </row>
-    <row r="95" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="95" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B95" s="41">
         <v>85</v>
       </c>
@@ -9192,7 +9525,7 @@
       </c>
       <c r="P95" s="44"/>
     </row>
-    <row r="96" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B96" s="41">
         <v>86</v>
       </c>
@@ -9223,7 +9556,7 @@
       </c>
       <c r="P96" s="44"/>
     </row>
-    <row r="97" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B97" s="41">
         <v>87</v>
       </c>
@@ -9254,7 +9587,7 @@
       </c>
       <c r="P97" s="44"/>
     </row>
-    <row r="98" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="98" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B98" s="41">
         <v>88</v>
       </c>
@@ -9285,7 +9618,7 @@
       </c>
       <c r="P98" s="44"/>
     </row>
-    <row r="99" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B99" s="41">
         <v>89</v>
       </c>
@@ -9316,7 +9649,7 @@
       </c>
       <c r="P99" s="44"/>
     </row>
-    <row r="100" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="100" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B100" s="41">
         <v>90</v>
       </c>
@@ -9347,7 +9680,7 @@
       </c>
       <c r="P100" s="44"/>
     </row>
-    <row r="101" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B101" s="41">
         <v>91</v>
       </c>
@@ -9378,7 +9711,7 @@
       </c>
       <c r="P101" s="44"/>
     </row>
-    <row r="102" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="102" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B102" s="41">
         <v>92</v>
       </c>
@@ -9409,7 +9742,7 @@
       </c>
       <c r="P102" s="44"/>
     </row>
-    <row r="103" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="103" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B103" s="41">
         <v>93</v>
       </c>
@@ -9440,7 +9773,7 @@
       </c>
       <c r="P103" s="44"/>
     </row>
-    <row r="104" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="104" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B104" s="41">
         <v>94</v>
       </c>
@@ -9471,7 +9804,7 @@
       </c>
       <c r="P104" s="44"/>
     </row>
-    <row r="105" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="105" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B105" s="41">
         <v>95</v>
       </c>
@@ -9502,7 +9835,7 @@
       </c>
       <c r="P105" s="44"/>
     </row>
-    <row r="106" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="106" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B106" s="41">
         <v>96</v>
       </c>
@@ -9533,7 +9866,7 @@
       </c>
       <c r="P106" s="44"/>
     </row>
-    <row r="107" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B107" s="41">
         <v>97</v>
       </c>
@@ -9564,7 +9897,7 @@
       </c>
       <c r="P107" s="44"/>
     </row>
-    <row r="108" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="108" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B108" s="41">
         <v>98</v>
       </c>
@@ -9595,7 +9928,7 @@
       </c>
       <c r="P108" s="44"/>
     </row>
-    <row r="109" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B109" s="41">
         <v>99</v>
       </c>
@@ -9626,7 +9959,7 @@
       </c>
       <c r="P109" s="44"/>
     </row>
-    <row r="110" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="110" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B110" s="41">
         <v>100</v>
       </c>
@@ -9744,49 +10077,49 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28A2F053-EB65-4682-A8B4-EF605DDDBF14}">
   <dimension ref="B2:P110"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.3046875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="15" width="18.69140625" customWidth="1"/>
-    <col min="16" max="16" width="64.53515625" customWidth="1"/>
+    <col min="3" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="64.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:16" x14ac:dyDescent="0.4">
-      <c r="C2" s="57" t="s">
-        <v>110</v>
-      </c>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="57"/>
-      <c r="L2" s="57"/>
-      <c r="M2" s="57"/>
-      <c r="N2" s="57"/>
-      <c r="O2" s="57"/>
-      <c r="P2" s="57"/>
-    </row>
-    <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C4" s="58" t="s">
+    <row r="2" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="C2" s="56" t="s">
+        <v>128</v>
+      </c>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="56"/>
+      <c r="M2" s="56"/>
+      <c r="N2" s="56"/>
+      <c r="O2" s="56"/>
+      <c r="P2" s="56"/>
+    </row>
+    <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C4" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="58"/>
-      <c r="L4" s="58"/>
-      <c r="M4" s="58"/>
-      <c r="N4" s="58"/>
-      <c r="O4" s="58"/>
-      <c r="P4" s="58"/>
-    </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="57"/>
+      <c r="L4" s="57"/>
+      <c r="M4" s="57"/>
+      <c r="N4" s="57"/>
+      <c r="O4" s="57"/>
+      <c r="P4" s="57"/>
+    </row>
+    <row r="5" spans="2:16" x14ac:dyDescent="0.25">
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
@@ -9802,8 +10135,8 @@
       <c r="O5" s="5"/>
       <c r="P5" s="5"/>
     </row>
-    <row r="6" spans="2:16" x14ac:dyDescent="0.4">
-      <c r="C6" s="55" t="s">
+    <row r="6" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="C6" s="58" t="s">
         <v>11</v>
       </c>
       <c r="D6" s="10" t="s">
@@ -9825,8 +10158,8 @@
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
     </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.4">
-      <c r="C7" s="55"/>
+    <row r="7" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="C7" s="58"/>
       <c r="D7" s="11" t="s">
         <v>13</v>
       </c>
@@ -9836,7 +10169,7 @@
       </c>
       <c r="J7" s="37"/>
     </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B9" s="6"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -9844,22 +10177,22 @@
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
-      <c r="I9" s="56" t="s">
+      <c r="I9" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="J9" s="56"/>
+      <c r="J9" s="59"/>
       <c r="K9" s="7"/>
-      <c r="L9" s="56" t="s">
+      <c r="L9" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="M9" s="56"/>
-      <c r="N9" s="56" t="s">
+      <c r="M9" s="59"/>
+      <c r="N9" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="O9" s="56"/>
+      <c r="O9" s="59"/>
       <c r="P9" s="7"/>
     </row>
-    <row r="10" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="8" t="s">
         <v>17</v>
       </c>
@@ -9906,7 +10239,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="41">
         <v>1</v>
       </c>
@@ -9937,7 +10270,7 @@
       </c>
       <c r="P11" s="44"/>
     </row>
-    <row r="12" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="41">
         <v>2</v>
       </c>
@@ -9968,7 +10301,7 @@
       </c>
       <c r="P12" s="44"/>
     </row>
-    <row r="13" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="41">
         <v>3</v>
       </c>
@@ -9999,7 +10332,7 @@
       </c>
       <c r="P13" s="44"/>
     </row>
-    <row r="14" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="41">
         <v>4</v>
       </c>
@@ -10030,7 +10363,7 @@
       </c>
       <c r="P14" s="44"/>
     </row>
-    <row r="15" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="41">
         <v>5</v>
       </c>
@@ -10061,7 +10394,7 @@
       </c>
       <c r="P15" s="44"/>
     </row>
-    <row r="16" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="41">
         <v>6</v>
       </c>
@@ -10092,7 +10425,7 @@
       </c>
       <c r="P16" s="44"/>
     </row>
-    <row r="17" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="41">
         <v>7</v>
       </c>
@@ -10123,7 +10456,7 @@
       </c>
       <c r="P17" s="44"/>
     </row>
-    <row r="18" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="41">
         <v>8</v>
       </c>
@@ -10154,7 +10487,7 @@
       </c>
       <c r="P18" s="44"/>
     </row>
-    <row r="19" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="41">
         <v>9</v>
       </c>
@@ -10185,7 +10518,7 @@
       </c>
       <c r="P19" s="44"/>
     </row>
-    <row r="20" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="41">
         <v>10</v>
       </c>
@@ -10216,7 +10549,7 @@
       </c>
       <c r="P20" s="44"/>
     </row>
-    <row r="21" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="41">
         <v>11</v>
       </c>
@@ -10247,7 +10580,7 @@
       </c>
       <c r="P21" s="44"/>
     </row>
-    <row r="22" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="41">
         <v>12</v>
       </c>
@@ -10278,7 +10611,7 @@
       </c>
       <c r="P22" s="44"/>
     </row>
-    <row r="23" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B23" s="41">
         <v>13</v>
       </c>
@@ -10309,7 +10642,7 @@
       </c>
       <c r="P23" s="44"/>
     </row>
-    <row r="24" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="41">
         <v>14</v>
       </c>
@@ -10340,7 +10673,7 @@
       </c>
       <c r="P24" s="44"/>
     </row>
-    <row r="25" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B25" s="41">
         <v>15</v>
       </c>
@@ -10371,7 +10704,7 @@
       </c>
       <c r="P25" s="44"/>
     </row>
-    <row r="26" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="41">
         <v>16</v>
       </c>
@@ -10402,7 +10735,7 @@
       </c>
       <c r="P26" s="44"/>
     </row>
-    <row r="27" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B27" s="41">
         <v>17</v>
       </c>
@@ -10433,7 +10766,7 @@
       </c>
       <c r="P27" s="44"/>
     </row>
-    <row r="28" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B28" s="41">
         <v>18</v>
       </c>
@@ -10464,7 +10797,7 @@
       </c>
       <c r="P28" s="44"/>
     </row>
-    <row r="29" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B29" s="41">
         <v>19</v>
       </c>
@@ -10495,7 +10828,7 @@
       </c>
       <c r="P29" s="44"/>
     </row>
-    <row r="30" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="41">
         <v>20</v>
       </c>
@@ -10526,7 +10859,7 @@
       </c>
       <c r="P30" s="44"/>
     </row>
-    <row r="31" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B31" s="41">
         <v>21</v>
       </c>
@@ -10557,7 +10890,7 @@
       </c>
       <c r="P31" s="44"/>
     </row>
-    <row r="32" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B32" s="41">
         <v>22</v>
       </c>
@@ -10588,7 +10921,7 @@
       </c>
       <c r="P32" s="44"/>
     </row>
-    <row r="33" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="41">
         <v>23</v>
       </c>
@@ -10619,7 +10952,7 @@
       </c>
       <c r="P33" s="44"/>
     </row>
-    <row r="34" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B34" s="41">
         <v>24</v>
       </c>
@@ -10650,7 +10983,7 @@
       </c>
       <c r="P34" s="44"/>
     </row>
-    <row r="35" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B35" s="41">
         <v>25</v>
       </c>
@@ -10681,7 +11014,7 @@
       </c>
       <c r="P35" s="44"/>
     </row>
-    <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="41">
         <v>26</v>
       </c>
@@ -10712,7 +11045,7 @@
       </c>
       <c r="P36" s="44"/>
     </row>
-    <row r="37" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="41">
         <v>27</v>
       </c>
@@ -10743,7 +11076,7 @@
       </c>
       <c r="P37" s="44"/>
     </row>
-    <row r="38" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B38" s="41">
         <v>28</v>
       </c>
@@ -10774,7 +11107,7 @@
       </c>
       <c r="P38" s="44"/>
     </row>
-    <row r="39" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B39" s="41">
         <v>29</v>
       </c>
@@ -10805,7 +11138,7 @@
       </c>
       <c r="P39" s="44"/>
     </row>
-    <row r="40" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B40" s="41">
         <v>30</v>
       </c>
@@ -10836,7 +11169,7 @@
       </c>
       <c r="P40" s="44"/>
     </row>
-    <row r="41" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B41" s="41">
         <v>31</v>
       </c>
@@ -10867,7 +11200,7 @@
       </c>
       <c r="P41" s="44"/>
     </row>
-    <row r="42" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B42" s="41">
         <v>32</v>
       </c>
@@ -10898,7 +11231,7 @@
       </c>
       <c r="P42" s="44"/>
     </row>
-    <row r="43" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B43" s="41">
         <v>33</v>
       </c>
@@ -10929,7 +11262,7 @@
       </c>
       <c r="P43" s="44"/>
     </row>
-    <row r="44" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B44" s="41">
         <v>34</v>
       </c>
@@ -10960,7 +11293,7 @@
       </c>
       <c r="P44" s="44"/>
     </row>
-    <row r="45" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B45" s="41">
         <v>35</v>
       </c>
@@ -10991,7 +11324,7 @@
       </c>
       <c r="P45" s="44"/>
     </row>
-    <row r="46" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B46" s="41">
         <v>36</v>
       </c>
@@ -11022,7 +11355,7 @@
       </c>
       <c r="P46" s="44"/>
     </row>
-    <row r="47" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B47" s="41">
         <v>37</v>
       </c>
@@ -11053,7 +11386,7 @@
       </c>
       <c r="P47" s="44"/>
     </row>
-    <row r="48" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B48" s="41">
         <v>38</v>
       </c>
@@ -11084,7 +11417,7 @@
       </c>
       <c r="P48" s="44"/>
     </row>
-    <row r="49" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B49" s="41">
         <v>39</v>
       </c>
@@ -11115,7 +11448,7 @@
       </c>
       <c r="P49" s="44"/>
     </row>
-    <row r="50" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B50" s="41">
         <v>40</v>
       </c>
@@ -11146,7 +11479,7 @@
       </c>
       <c r="P50" s="44"/>
     </row>
-    <row r="51" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B51" s="41">
         <v>41</v>
       </c>
@@ -11177,7 +11510,7 @@
       </c>
       <c r="P51" s="44"/>
     </row>
-    <row r="52" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B52" s="41">
         <v>42</v>
       </c>
@@ -11208,7 +11541,7 @@
       </c>
       <c r="P52" s="44"/>
     </row>
-    <row r="53" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B53" s="41">
         <v>43</v>
       </c>
@@ -11239,7 +11572,7 @@
       </c>
       <c r="P53" s="44"/>
     </row>
-    <row r="54" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B54" s="41">
         <v>44</v>
       </c>
@@ -11270,7 +11603,7 @@
       </c>
       <c r="P54" s="44"/>
     </row>
-    <row r="55" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="55" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B55" s="41">
         <v>45</v>
       </c>
@@ -11301,7 +11634,7 @@
       </c>
       <c r="P55" s="44"/>
     </row>
-    <row r="56" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B56" s="41">
         <v>46</v>
       </c>
@@ -11332,7 +11665,7 @@
       </c>
       <c r="P56" s="44"/>
     </row>
-    <row r="57" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B57" s="41">
         <v>47</v>
       </c>
@@ -11363,7 +11696,7 @@
       </c>
       <c r="P57" s="44"/>
     </row>
-    <row r="58" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B58" s="41">
         <v>48</v>
       </c>
@@ -11394,7 +11727,7 @@
       </c>
       <c r="P58" s="44"/>
     </row>
-    <row r="59" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B59" s="41">
         <v>49</v>
       </c>
@@ -11425,7 +11758,7 @@
       </c>
       <c r="P59" s="44"/>
     </row>
-    <row r="60" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B60" s="41">
         <v>50</v>
       </c>
@@ -11456,7 +11789,7 @@
       </c>
       <c r="P60" s="44"/>
     </row>
-    <row r="61" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B61" s="41">
         <v>51</v>
       </c>
@@ -11487,7 +11820,7 @@
       </c>
       <c r="P61" s="44"/>
     </row>
-    <row r="62" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B62" s="41">
         <v>52</v>
       </c>
@@ -11518,7 +11851,7 @@
       </c>
       <c r="P62" s="44"/>
     </row>
-    <row r="63" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B63" s="41">
         <v>53</v>
       </c>
@@ -11549,7 +11882,7 @@
       </c>
       <c r="P63" s="44"/>
     </row>
-    <row r="64" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B64" s="41">
         <v>54</v>
       </c>
@@ -11580,7 +11913,7 @@
       </c>
       <c r="P64" s="44"/>
     </row>
-    <row r="65" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B65" s="41">
         <v>55</v>
       </c>
@@ -11611,7 +11944,7 @@
       </c>
       <c r="P65" s="44"/>
     </row>
-    <row r="66" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B66" s="41">
         <v>56</v>
       </c>
@@ -11642,7 +11975,7 @@
       </c>
       <c r="P66" s="44"/>
     </row>
-    <row r="67" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B67" s="41">
         <v>57</v>
       </c>
@@ -11673,7 +12006,7 @@
       </c>
       <c r="P67" s="44"/>
     </row>
-    <row r="68" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B68" s="41">
         <v>58</v>
       </c>
@@ -11704,7 +12037,7 @@
       </c>
       <c r="P68" s="44"/>
     </row>
-    <row r="69" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B69" s="41">
         <v>59</v>
       </c>
@@ -11735,7 +12068,7 @@
       </c>
       <c r="P69" s="44"/>
     </row>
-    <row r="70" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B70" s="41">
         <v>60</v>
       </c>
@@ -11766,7 +12099,7 @@
       </c>
       <c r="P70" s="44"/>
     </row>
-    <row r="71" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B71" s="41">
         <v>61</v>
       </c>
@@ -11797,7 +12130,7 @@
       </c>
       <c r="P71" s="44"/>
     </row>
-    <row r="72" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B72" s="41">
         <v>62</v>
       </c>
@@ -11828,7 +12161,7 @@
       </c>
       <c r="P72" s="44"/>
     </row>
-    <row r="73" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B73" s="41">
         <v>63</v>
       </c>
@@ -11859,7 +12192,7 @@
       </c>
       <c r="P73" s="44"/>
     </row>
-    <row r="74" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B74" s="41">
         <v>64</v>
       </c>
@@ -11890,7 +12223,7 @@
       </c>
       <c r="P74" s="44"/>
     </row>
-    <row r="75" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B75" s="41">
         <v>65</v>
       </c>
@@ -11921,7 +12254,7 @@
       </c>
       <c r="P75" s="44"/>
     </row>
-    <row r="76" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B76" s="41">
         <v>66</v>
       </c>
@@ -11952,7 +12285,7 @@
       </c>
       <c r="P76" s="44"/>
     </row>
-    <row r="77" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B77" s="41">
         <v>67</v>
       </c>
@@ -11983,7 +12316,7 @@
       </c>
       <c r="P77" s="44"/>
     </row>
-    <row r="78" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B78" s="41">
         <v>68</v>
       </c>
@@ -12014,7 +12347,7 @@
       </c>
       <c r="P78" s="44"/>
     </row>
-    <row r="79" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B79" s="41">
         <v>69</v>
       </c>
@@ -12045,7 +12378,7 @@
       </c>
       <c r="P79" s="44"/>
     </row>
-    <row r="80" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B80" s="41">
         <v>70</v>
       </c>
@@ -12076,7 +12409,7 @@
       </c>
       <c r="P80" s="44"/>
     </row>
-    <row r="81" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B81" s="41">
         <v>71</v>
       </c>
@@ -12107,7 +12440,7 @@
       </c>
       <c r="P81" s="44"/>
     </row>
-    <row r="82" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B82" s="41">
         <v>72</v>
       </c>
@@ -12138,7 +12471,7 @@
       </c>
       <c r="P82" s="44"/>
     </row>
-    <row r="83" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B83" s="41">
         <v>73</v>
       </c>
@@ -12169,7 +12502,7 @@
       </c>
       <c r="P83" s="44"/>
     </row>
-    <row r="84" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B84" s="41">
         <v>74</v>
       </c>
@@ -12200,7 +12533,7 @@
       </c>
       <c r="P84" s="44"/>
     </row>
-    <row r="85" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B85" s="41">
         <v>75</v>
       </c>
@@ -12231,7 +12564,7 @@
       </c>
       <c r="P85" s="44"/>
     </row>
-    <row r="86" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B86" s="41">
         <v>76</v>
       </c>
@@ -12262,7 +12595,7 @@
       </c>
       <c r="P86" s="44"/>
     </row>
-    <row r="87" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B87" s="41">
         <v>77</v>
       </c>
@@ -12293,7 +12626,7 @@
       </c>
       <c r="P87" s="44"/>
     </row>
-    <row r="88" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B88" s="41">
         <v>78</v>
       </c>
@@ -12324,7 +12657,7 @@
       </c>
       <c r="P88" s="44"/>
     </row>
-    <row r="89" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B89" s="41">
         <v>79</v>
       </c>
@@ -12355,7 +12688,7 @@
       </c>
       <c r="P89" s="44"/>
     </row>
-    <row r="90" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B90" s="41">
         <v>80</v>
       </c>
@@ -12386,7 +12719,7 @@
       </c>
       <c r="P90" s="44"/>
     </row>
-    <row r="91" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="91" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B91" s="41">
         <v>81</v>
       </c>
@@ -12417,7 +12750,7 @@
       </c>
       <c r="P91" s="44"/>
     </row>
-    <row r="92" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B92" s="41">
         <v>82</v>
       </c>
@@ -12448,7 +12781,7 @@
       </c>
       <c r="P92" s="44"/>
     </row>
-    <row r="93" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="93" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B93" s="41">
         <v>83</v>
       </c>
@@ -12479,7 +12812,7 @@
       </c>
       <c r="P93" s="44"/>
     </row>
-    <row r="94" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B94" s="41">
         <v>84</v>
       </c>
@@ -12510,7 +12843,7 @@
       </c>
       <c r="P94" s="44"/>
     </row>
-    <row r="95" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="95" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B95" s="41">
         <v>85</v>
       </c>
@@ -12541,7 +12874,7 @@
       </c>
       <c r="P95" s="44"/>
     </row>
-    <row r="96" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B96" s="41">
         <v>86</v>
       </c>
@@ -12572,7 +12905,7 @@
       </c>
       <c r="P96" s="44"/>
     </row>
-    <row r="97" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B97" s="41">
         <v>87</v>
       </c>
@@ -12603,7 +12936,7 @@
       </c>
       <c r="P97" s="44"/>
     </row>
-    <row r="98" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="98" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B98" s="41">
         <v>88</v>
       </c>
@@ -12634,7 +12967,7 @@
       </c>
       <c r="P98" s="44"/>
     </row>
-    <row r="99" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B99" s="41">
         <v>89</v>
       </c>
@@ -12665,7 +12998,7 @@
       </c>
       <c r="P99" s="44"/>
     </row>
-    <row r="100" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="100" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B100" s="41">
         <v>90</v>
       </c>
@@ -12696,7 +13029,7 @@
       </c>
       <c r="P100" s="44"/>
     </row>
-    <row r="101" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B101" s="41">
         <v>91</v>
       </c>
@@ -12727,7 +13060,7 @@
       </c>
       <c r="P101" s="44"/>
     </row>
-    <row r="102" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="102" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B102" s="41">
         <v>92</v>
       </c>
@@ -12758,7 +13091,7 @@
       </c>
       <c r="P102" s="44"/>
     </row>
-    <row r="103" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="103" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B103" s="41">
         <v>93</v>
       </c>
@@ -12789,7 +13122,7 @@
       </c>
       <c r="P103" s="44"/>
     </row>
-    <row r="104" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="104" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B104" s="41">
         <v>94</v>
       </c>
@@ -12820,7 +13153,7 @@
       </c>
       <c r="P104" s="44"/>
     </row>
-    <row r="105" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="105" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B105" s="41">
         <v>95</v>
       </c>
@@ -12851,7 +13184,7 @@
       </c>
       <c r="P105" s="44"/>
     </row>
-    <row r="106" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="106" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B106" s="41">
         <v>96</v>
       </c>
@@ -12882,7 +13215,7 @@
       </c>
       <c r="P106" s="44"/>
     </row>
-    <row r="107" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B107" s="41">
         <v>97</v>
       </c>
@@ -12913,7 +13246,7 @@
       </c>
       <c r="P107" s="44"/>
     </row>
-    <row r="108" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="108" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B108" s="41">
         <v>98</v>
       </c>
@@ -12944,7 +13277,7 @@
       </c>
       <c r="P108" s="44"/>
     </row>
-    <row r="109" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B109" s="41">
         <v>99</v>
       </c>
@@ -12975,7 +13308,7 @@
       </c>
       <c r="P109" s="44"/>
     </row>
-    <row r="110" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="110" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B110" s="41">
         <v>100</v>
       </c>
@@ -13093,60 +13426,60 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6230FA8A-EA33-4C76-AA54-C885D607690C}">
   <dimension ref="B2:J39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.3046875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="10" width="22.15234375" customWidth="1"/>
+    <col min="2" max="10" width="22.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B2" s="57" t="s">
-        <v>111</v>
-      </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B4" s="58" t="s">
-        <v>112</v>
-      </c>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B5" s="58"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="58"/>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B6" s="58"/>
-      <c r="C6" s="58"/>
-      <c r="D6" s="58"/>
-      <c r="E6" s="58"/>
-      <c r="F6" s="58"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="58"/>
-      <c r="I6" s="58"/>
-      <c r="J6" s="58"/>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B2" s="56" t="s">
+        <v>129</v>
+      </c>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B4" s="57" t="s">
+        <v>130</v>
+      </c>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B5" s="57"/>
+      <c r="C5" s="57"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="57"/>
+      <c r="H5" s="57"/>
+      <c r="I5" s="57"/>
+      <c r="J5" s="57"/>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B6" s="57"/>
+      <c r="C6" s="57"/>
+      <c r="D6" s="57"/>
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="57"/>
+      <c r="H6" s="57"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
@@ -13157,9 +13490,9 @@
       <c r="I7" s="5"/>
       <c r="J7" s="5"/>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B8" s="25" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="C8" s="12"/>
       <c r="D8" s="12"/>
@@ -13170,7 +13503,7 @@
       <c r="I8" s="12"/>
       <c r="J8" s="12"/>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="13" t="s">
         <v>31</v>
       </c>
@@ -13183,7 +13516,7 @@
       <c r="I9" s="12"/>
       <c r="J9" s="12"/>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B10" s="13" t="s">
         <v>53</v>
       </c>
@@ -13196,7 +13529,7 @@
       <c r="I10" s="12"/>
       <c r="J10" s="12"/>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="13" t="s">
         <v>38</v>
       </c>
@@ -13209,7 +13542,7 @@
       <c r="I11" s="12"/>
       <c r="J11" s="12"/>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B12" s="13" t="s">
         <v>58</v>
       </c>
@@ -13222,7 +13555,7 @@
       <c r="I12" s="12"/>
       <c r="J12" s="12"/>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="13" t="s">
         <v>61</v>
       </c>
@@ -13235,7 +13568,7 @@
       <c r="I13" s="12"/>
       <c r="J13" s="12"/>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B14" s="14" t="s">
         <v>66</v>
       </c>
@@ -13248,7 +13581,7 @@
       <c r="I14" s="12"/>
       <c r="J14" s="12"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="3"/>
       <c r="C15" s="12"/>
       <c r="D15" s="12"/>
@@ -13259,9 +13592,9 @@
       <c r="I15" s="12"/>
       <c r="J15" s="12"/>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="26" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="C16" s="12"/>
       <c r="D16" s="12"/>
@@ -13272,9 +13605,9 @@
       <c r="I16" s="12"/>
       <c r="J16" s="12"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -13285,9 +13618,9 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -13298,9 +13631,9 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="16" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -13311,7 +13644,7 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="3"/>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -13322,9 +13655,9 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="26" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
@@ -13335,7 +13668,7 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="17">
         <v>45658</v>
       </c>
@@ -13348,9 +13681,9 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="18" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
@@ -13361,7 +13694,7 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="12"/>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
@@ -13372,15 +13705,15 @@
       <c r="I24" s="12"/>
       <c r="J24" s="12"/>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="27" t="s">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="C25" s="28" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="D25" s="28" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="E25" s="29"/>
       <c r="F25" s="29"/>
@@ -13389,7 +13722,7 @@
       <c r="I25" s="29"/>
       <c r="J25" s="30"/>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="19" t="s">
         <v>75</v>
       </c>
@@ -13400,10 +13733,10 @@
         <v>76</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="G26" s="12" t="s">
         <v>102</v>
@@ -13412,7 +13745,7 @@
       <c r="I26" s="12"/>
       <c r="J26" s="20"/>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="19" t="s">
         <v>32</v>
       </c>
@@ -13429,7 +13762,7 @@
         <v>33</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="H27" s="12" t="s">
         <v>35</v>
@@ -13439,21 +13772,21 @@
       </c>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="19" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="C28" s="51">
         <v>40</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="G28" s="12" t="s">
         <v>35</v>
@@ -13464,7 +13797,7 @@
       <c r="I28" s="12"/>
       <c r="J28" s="20"/>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="19" t="s">
         <v>39</v>
       </c>
@@ -13472,7 +13805,7 @@
         <v>25</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="E29" s="12" t="s">
         <v>40</v>
@@ -13491,24 +13824,24 @@
       </c>
       <c r="J29" s="20"/>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="19" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="C30" s="51">
         <v>30</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="H30" s="12" t="s">
         <v>35</v>
@@ -13518,27 +13851,27 @@
       </c>
       <c r="J30" s="20"/>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" s="21" t="s">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="C31" s="51">
         <v>30</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>140</v>
+        <v>158</v>
       </c>
       <c r="H31" s="12" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="I31" s="12" t="s">
         <v>35</v>
@@ -13547,9 +13880,9 @@
         <v>102</v>
       </c>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="22" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="C32" s="52">
         <v>10</v>
@@ -13564,7 +13897,7 @@
       <c r="I32" s="23"/>
       <c r="J32" s="24"/>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="12"/>
       <c r="C33" s="12"/>
       <c r="D33" s="12"/>
@@ -13575,12 +13908,12 @@
       <c r="I33" s="12"/>
       <c r="J33" s="12"/>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="33" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="C34" s="34" t="s">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="D34" s="12"/>
       <c r="E34" s="12"/>
@@ -13590,12 +13923,12 @@
       <c r="I34" s="12"/>
       <c r="J34" s="12"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="21" t="s">
         <v>30</v>
       </c>
       <c r="C35" s="31" t="s">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="D35" s="12"/>
       <c r="E35" s="12"/>
@@ -13605,12 +13938,12 @@
       <c r="I35" s="12"/>
       <c r="J35" s="12"/>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="21" t="s">
         <v>37</v>
       </c>
       <c r="C36" s="20" t="s">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="D36" s="12"/>
       <c r="E36" s="12"/>
@@ -13620,12 +13953,12 @@
       <c r="I36" s="12"/>
       <c r="J36" s="12"/>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="21" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="C37" s="20" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="D37" s="12"/>
       <c r="E37" s="12"/>
@@ -13635,12 +13968,12 @@
       <c r="I37" s="12"/>
       <c r="J37" s="12"/>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="21" t="s">
         <v>74</v>
       </c>
       <c r="C38" s="20" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="D38" s="12"/>
       <c r="E38" s="12"/>
@@ -13650,12 +13983,12 @@
       <c r="I38" s="12"/>
       <c r="J38" s="12"/>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="32" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="C39" s="24" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="D39" s="12"/>
       <c r="E39" s="12"/>
@@ -13676,23 +14009,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="03ae2d87-6db6-4be4-88e5-dbaddc28be73" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100DD5D270F165CDC4A813E57A434418B09" ma:contentTypeVersion="13" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="6ed8c571966b9827c2f4c920c5f93c32">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="03ae2d87-6db6-4be4-88e5-dbaddc28be73" xmlns:ns4="f9914671-1c67-425d-8130-55177899a278" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d3c60be3fe4143b94f946cc5c4a96dc8" ns3:_="" ns4:_="">
     <xsd:import namespace="03ae2d87-6db6-4be4-88e5-dbaddc28be73"/>
@@ -13911,32 +14227,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62A9DD66-DB84-4B71-BBB5-740469C343F7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="f9914671-1c67-425d-8130-55177899a278"/>
-    <ds:schemaRef ds:uri="03ae2d87-6db6-4be4-88e5-dbaddc28be73"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66922CC8-4B98-4DC4-8316-4B594EF99561}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="03ae2d87-6db6-4be4-88e5-dbaddc28be73" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EBF4B177-136A-4B5E-9CEE-7C2817EBEF9A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -13953,4 +14261,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66922CC8-4B98-4DC4-8316-4B594EF99561}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62A9DD66-DB84-4B71-BBB5-740469C343F7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="03ae2d87-6db6-4be4-88e5-dbaddc28be73"/>
+    <ds:schemaRef ds:uri="f9914671-1c67-425d-8130-55177899a278"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>